--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22128,10 +22128,10 @@
         <v>0</v>
       </c>
       <c r="AG110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.31</v>
+        <v>1.99</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.68</v>
+        <v>4.12</v>
       </c>
       <c r="R112" t="n">
-        <v>2.27</v>
+        <v>3.7</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,16 +22516,16 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="R114" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,16 +22910,16 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="R115" t="n">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF159" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF173" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.28</v>
+        <v>1.22</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.42</v>
+        <v>6.3</v>
       </c>
       <c r="R175" t="n">
-        <v>2.98</v>
+        <v>11.2</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34927,10 +34927,10 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF175" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF186" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF190" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF192" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF209" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH225" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -46944,10 +46944,10 @@
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47296,130 +47296,130 @@
         <v>1.95</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R238" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="S238" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="T238" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="U238" t="n">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="V238" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W238" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X238" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y238" t="n">
         <v>1.28</v>
       </c>
-      <c r="W238" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X238" t="n">
+      <c r="Z238" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA238" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB238" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC238" t="n">
         <v>2.36</v>
       </c>
-      <c r="Y238" t="n">
+      <c r="BD238" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE238" t="n">
         <v>1.51</v>
       </c>
-      <c r="Z238" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA238" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB238" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC238" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD238" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE238" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF238" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG238" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH238" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI238" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AJ238" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK238" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL238" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM238" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN238" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP238" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ238" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR238" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AS238" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT238" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AU238" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV238" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW238" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX238" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY238" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ238" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA238" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB238" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC238" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD238" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE238" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BF238" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="BG238" t="n">
         <v>0</v>
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,133 +47490,133 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R239" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="S239" t="n">
-        <v>4.28</v>
+        <v>2.62</v>
       </c>
       <c r="T239" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="U239" t="n">
-        <v>2.51</v>
+        <v>3.92</v>
       </c>
       <c r="V239" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W239" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X239" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AU239" t="n">
         <v>2.98</v>
       </c>
-      <c r="X239" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y239" t="n">
+      <c r="AV239" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX239" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z239" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA239" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB239" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC239" t="n">
+      <c r="AY239" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD239" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AE239" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF239" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG239" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH239" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI239" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ239" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK239" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL239" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM239" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN239" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO239" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP239" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ239" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR239" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS239" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT239" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AU239" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV239" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW239" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX239" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY239" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AZ239" t="n">
-        <v>2.79</v>
+        <v>1.58</v>
       </c>
       <c r="BA239" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="BB239" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC239" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="BD239" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="BE239" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="BF239" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="BG239" t="n">
         <v>0</v>
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,133 +47687,133 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R240" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="S240" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="T240" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="U240" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="V240" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W240" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="X240" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Y240" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z240" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AA240" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC240" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY240" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD240" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE240" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF240" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG240" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH240" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI240" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ240" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK240" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL240" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM240" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN240" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO240" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP240" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ240" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR240" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS240" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT240" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AU240" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV240" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW240" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX240" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY240" t="n">
+      <c r="AZ240" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BA240" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BB240" t="n">
         <v>1.17</v>
       </c>
-      <c r="AZ240" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BA240" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB240" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC240" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="BD240" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="BE240" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="BF240" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BG240" t="n">
         <v>0</v>
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,133 +47884,133 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="R241" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="S241" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T241" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U241" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V241" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W241" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X241" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z241" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA241" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB241" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC241" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD241" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AF241" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AG241" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="AH241" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI241" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ241" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK241" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL241" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM241" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN241" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO241" t="n">
         <v>0</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR241" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS241" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AT241" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV241" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW241" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AX241" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AY241" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ241" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA241" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BB241" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC241" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BD241" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE241" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF241" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG241" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,133 +48081,133 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R242" t="n">
-        <v>7.65</v>
+        <v>2.55</v>
       </c>
       <c r="S242" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T242" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U242" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V242" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W242" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X242" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y242" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z242" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA242" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB242" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC242" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD242" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF242" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG242" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH242" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI242" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ242" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK242" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL242" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM242" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN242" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO242" t="n">
         <v>0</v>
       </c>
       <c r="AP242" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ242" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR242" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS242" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AU242" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV242" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW242" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX242" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY242" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ242" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB242" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC242" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD242" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE242" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF242" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG242" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,133 +48869,133 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S246" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T246" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U246" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V246" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W246" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X246" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y246" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA246" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB246" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC246" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD246" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE246" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF246" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG246" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH246" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI246" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ246" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK246" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL246" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM246" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN246" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO246" t="n">
         <v>0</v>
       </c>
       <c r="AP246" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ246" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR246" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS246" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU246" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV246" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW246" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX246" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY246" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ246" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA246" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB246" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC246" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD246" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE246" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF246" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG246" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,133 +49263,133 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T248" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U248" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V248" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W248" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X248" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z248" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB248" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC248" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD248" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH248" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI248" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ248" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK248" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL248" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM248" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN248" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO248" t="n">
         <v>0</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR248" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS248" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT248" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV248" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW248" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX248" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY248" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ248" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA248" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB248" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC248" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD248" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE248" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF248" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG248" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,13 +53006,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q267" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -53051,10 +53051,10 @@
         <v>0</v>
       </c>
       <c r="AE267" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF267" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG267" t="n">
         <v>0</v>
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,55 +53203,55 @@
         </is>
       </c>
       <c r="P268" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R268" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S268" t="n">
+        <v>0</v>
+      </c>
+      <c r="T268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="n">
+        <v>0</v>
+      </c>
+      <c r="V268" t="n">
+        <v>0</v>
+      </c>
+      <c r="W268" t="n">
+        <v>0</v>
+      </c>
+      <c r="X268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF268" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q268" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R268" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="S268" t="n">
-        <v>0</v>
-      </c>
-      <c r="T268" t="n">
-        <v>0</v>
-      </c>
-      <c r="U268" t="n">
-        <v>0</v>
-      </c>
-      <c r="V268" t="n">
-        <v>0</v>
-      </c>
-      <c r="W268" t="n">
-        <v>0</v>
-      </c>
-      <c r="X268" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y268" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z268" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA268" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB268" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC268" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD268" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE268" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF268" t="n">
-        <v>2.2</v>
       </c>
       <c r="AG268" t="n">
         <v>0</v>
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53597,13 +53597,13 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q270" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R270" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -53642,10 +53642,10 @@
         <v>0</v>
       </c>
       <c r="AE270" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF270" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG270" t="n">
         <v>0</v>
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF272" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54233,10 +54233,10 @@
         <v>0</v>
       </c>
       <c r="AE273" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF273" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,22 +55519,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,22 +55716,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q281" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF283" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q284" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF284" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q291" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q293" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF293" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q303" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R303" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60143,10 +60143,10 @@
         <v>0</v>
       </c>
       <c r="AE303" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF303" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="Q304" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R304" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60340,10 +60340,10 @@
         <v>0</v>
       </c>
       <c r="AE304" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AF304" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -60444,7 +60444,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60492,13 +60492,13 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q305" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R305" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
@@ -60537,10 +60537,10 @@
         <v>0</v>
       </c>
       <c r="AE305" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF305" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG305" t="n">
         <v>0</v>
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60689,13 +60689,13 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="Q306" t="n">
-        <v>6.1</v>
+        <v>3.58</v>
       </c>
       <c r="R306" t="n">
-        <v>6.63</v>
+        <v>3.1</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
@@ -60734,10 +60734,10 @@
         <v>0</v>
       </c>
       <c r="AE306" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF306" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG306" t="n">
         <v>0</v>
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q307" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R307" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61083,13 +61083,13 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q308" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R308" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -61128,10 +61128,10 @@
         <v>0</v>
       </c>
       <c r="AE308" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF308" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG308" t="n">
         <v>0</v>
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61280,13 +61280,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q309" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R309" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -61325,10 +61325,10 @@
         <v>0</v>
       </c>
       <c r="AE309" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF309" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG309" t="n">
         <v>0</v>
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,22 +62020,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62064,7 +62064,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -62414,22 +62414,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62458,7 +62458,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,7 +62808,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>3.43</v>
+        <v>1.89</v>
       </c>
       <c r="Q319" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="R319" t="n">
-        <v>2.04</v>
+        <v>3.93</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63301,10 +63301,10 @@
         <v>0</v>
       </c>
       <c r="AG319" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH319" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI319" t="n">
         <v>0</v>
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1.89</v>
+        <v>3.43</v>
       </c>
       <c r="Q321" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="R321" t="n">
-        <v>3.93</v>
+        <v>2.04</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63695,10 +63695,10 @@
         <v>0</v>
       </c>
       <c r="AG321" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH321" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI321" t="n">
         <v>0</v>

--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2231,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.99</v>
+        <v>3.31</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.12</v>
+        <v>3.68</v>
       </c>
       <c r="R112" t="n">
-        <v>3.7</v>
+        <v>2.27</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,16 +22516,16 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG112" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.54</v>
+        <v>2.65</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="R113" t="n">
-        <v>6.3</v>
+        <v>2.65</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,16 +22713,16 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG113" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.65</v>
+        <v>1.54</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.82</v>
+        <v>4.88</v>
       </c>
       <c r="R114" t="n">
-        <v>2.65</v>
+        <v>6.3</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,16 +22910,16 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.31</v>
+        <v>1.99</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.68</v>
+        <v>4.12</v>
       </c>
       <c r="R115" t="n">
-        <v>2.27</v>
+        <v>3.7</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,16 +23107,16 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.28</v>
+        <v>4.98</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.42</v>
+        <v>4.12</v>
       </c>
       <c r="R135" t="n">
-        <v>2.98</v>
+        <v>1.75</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF135" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF153" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF159" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF168" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF171" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.62</v>
+        <v>4.3</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.27</v>
+        <v>3.57</v>
       </c>
       <c r="R182" t="n">
-        <v>5.3</v>
+        <v>1.81</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF182" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF186" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF209" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45374,10 +45374,10 @@
         <v>0</v>
       </c>
       <c r="AG228" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH228" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q233" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,133 +46505,133 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R234" t="n">
-        <v>7.65</v>
+        <v>3.4</v>
       </c>
       <c r="S234" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T234" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U234" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V234" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W234" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X234" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y234" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB234" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC234" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD234" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE234" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF234" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG234" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="AH234" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI234" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ234" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK234" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL234" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM234" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN234" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO234" t="n">
         <v>0</v>
       </c>
       <c r="AP234" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR234" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS234" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AU234" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV234" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW234" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AX234" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY234" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ234" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA234" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BB234" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC234" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD234" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE234" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF234" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG234" t="n">
         <v>0</v>
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,133 +46702,133 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S235" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T235" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U235" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V235" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W235" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X235" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA235" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB235" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC235" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD235" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE235" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF235" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG235" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH235" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI235" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ235" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK235" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL235" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM235" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN235" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO235" t="n">
         <v>0</v>
       </c>
       <c r="AP235" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR235" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS235" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AU235" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV235" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW235" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX235" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY235" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ235" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB235" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC235" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD235" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE235" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF235" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG235" t="n">
         <v>0</v>
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q236" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,133 +47293,133 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R238" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="S238" t="n">
-        <v>2.43</v>
+        <v>4.28</v>
       </c>
       <c r="T238" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="U238" t="n">
-        <v>4.45</v>
+        <v>2.51</v>
       </c>
       <c r="V238" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W238" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="X238" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Y238" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z238" t="n">
-        <v>8.9</v>
+        <v>6.55</v>
       </c>
       <c r="AA238" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB238" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC238" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AD238" t="n">
-        <v>2.74</v>
+        <v>3.76</v>
       </c>
       <c r="AE238" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AF238" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AG238" t="n">
-        <v>4.08</v>
+        <v>2.97</v>
       </c>
       <c r="AH238" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AI238" t="n">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ238" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK238" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL238" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW238" t="n">
         <v>1.75</v>
       </c>
-      <c r="AM238" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN238" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP238" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ238" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AR238" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS238" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AT238" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AU238" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV238" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW238" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AX238" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AY238" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AZ238" t="n">
-        <v>1.81</v>
+        <v>2.79</v>
       </c>
       <c r="BA238" t="n">
-        <v>2.56</v>
+        <v>1.58</v>
       </c>
       <c r="BB238" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BC238" t="n">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="BD238" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="BE238" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BF238" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG238" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,133 +47687,133 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="T240" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U240" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V240" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W240" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X240" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC240" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD240" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF240" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG240" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH240" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI240" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ240" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK240" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL240" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM240" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN240" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO240" t="n">
         <v>0</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR240" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS240" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT240" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV240" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW240" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX240" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY240" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ240" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BA240" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BB240" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC240" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD240" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE240" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF240" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG240" t="n">
         <v>0</v>
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,133 +48081,133 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="R242" t="n">
-        <v>2.55</v>
+        <v>3.27</v>
       </c>
       <c r="S242" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T242" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U242" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V242" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W242" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X242" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z242" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA242" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB242" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC242" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD242" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF242" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG242" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH242" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI242" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ242" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK242" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL242" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AM242" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN242" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO242" t="n">
         <v>0</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR242" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AS242" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AT242" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AU242" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV242" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AW242" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX242" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY242" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ242" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BA242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB242" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC242" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD242" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BE242" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF242" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG242" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,133 +48869,133 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T246" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U246" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V246" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W246" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X246" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z246" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA246" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB246" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC246" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD246" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF246" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG246" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH246" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI246" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ246" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK246" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL246" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM246" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN246" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO246" t="n">
         <v>0</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR246" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS246" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT246" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU246" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV246" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW246" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX246" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY246" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ246" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA246" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB246" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC246" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD246" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE246" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF246" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG246" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,133 +49460,133 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2.2</v>
+        <v>5.41</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="R249" t="n">
-        <v>3.27</v>
+        <v>1.53</v>
       </c>
       <c r="S249" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T249" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U249" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V249" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W249" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X249" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y249" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z249" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA249" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB249" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC249" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD249" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE249" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AF249" t="n">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="AG249" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH249" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI249" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ249" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK249" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL249" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM249" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN249" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO249" t="n">
         <v>0</v>
       </c>
       <c r="AP249" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ249" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR249" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS249" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU249" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV249" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW249" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX249" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY249" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ249" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA249" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB249" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC249" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD249" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE249" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF249" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG249" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q260" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52460,10 +52460,10 @@
         <v>0</v>
       </c>
       <c r="AE264" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF264" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52612,13 +52612,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q265" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -52657,10 +52657,10 @@
         <v>0</v>
       </c>
       <c r="AE265" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF265" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG265" t="n">
         <v>0</v>
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,13 +53203,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q268" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -53248,10 +53248,10 @@
         <v>0</v>
       </c>
       <c r="AE268" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF268" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG268" t="n">
         <v>0</v>
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53597,13 +53597,13 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q270" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -53642,10 +53642,10 @@
         <v>0</v>
       </c>
       <c r="AE270" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF270" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG270" t="n">
         <v>0</v>
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF272" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54233,10 +54233,10 @@
         <v>0</v>
       </c>
       <c r="AE273" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF273" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q276" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q277" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55716,22 +55716,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -56110,22 +56110,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R284" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56504,22 +56504,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF285" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q291" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R291" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57779,10 +57779,10 @@
         <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF291" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG291" t="n">
         <v>0</v>
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q292" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="Q293" t="n">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="R293" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF293" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q303" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R303" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60143,10 +60143,10 @@
         <v>0</v>
       </c>
       <c r="AE303" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF303" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="Q304" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R304" t="n">
-        <v>3.6</v>
+        <v>4.32</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60340,10 +60340,10 @@
         <v>0</v>
       </c>
       <c r="AE304" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AF304" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60689,13 +60689,13 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="Q306" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R306" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
@@ -60734,10 +60734,10 @@
         <v>0</v>
       </c>
       <c r="AE306" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AF306" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AG306" t="n">
         <v>0</v>
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="Q307" t="n">
-        <v>6.1</v>
+        <v>3.58</v>
       </c>
       <c r="R307" t="n">
-        <v>6.63</v>
+        <v>3.1</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -60931,10 +60931,10 @@
         <v>0</v>
       </c>
       <c r="AE307" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF307" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG307" t="n">
         <v>0</v>
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61083,13 +61083,13 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q308" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R308" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -61128,10 +61128,10 @@
         <v>0</v>
       </c>
       <c r="AE308" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF308" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG308" t="n">
         <v>0</v>
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61280,13 +61280,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="Q309" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="R309" t="n">
-        <v>4.32</v>
+        <v>6.63</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -61325,10 +61325,10 @@
         <v>0</v>
       </c>
       <c r="AE309" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF309" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG309" t="n">
         <v>0</v>
@@ -62020,22 +62020,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62064,7 +62064,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -62217,7 +62217,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62808,22 +62808,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -62852,7 +62852,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q319" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63301,10 +63301,10 @@
         <v>0</v>
       </c>
       <c r="AG319" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH319" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI319" t="n">
         <v>0</v>
@@ -63399,7 +63399,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -63409,12 +63409,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -63447,13 +63447,13 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q320" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R320" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>3.43</v>
+        <v>1.56</v>
       </c>
       <c r="Q321" t="n">
-        <v>4.02</v>
+        <v>4.58</v>
       </c>
       <c r="R321" t="n">
-        <v>2.04</v>
+        <v>5.82</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63689,10 +63689,10 @@
         <v>0</v>
       </c>
       <c r="AE321" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF321" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG321" t="n">
         <v>0</v>
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="Q322" t="n">
-        <v>4.58</v>
+        <v>4.03</v>
       </c>
       <c r="R322" t="n">
-        <v>5.82</v>
+        <v>3.93</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,16 +63886,16 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF322" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG322" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH322" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI322" t="n">
         <v>0</v>

--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22128,10 +22128,10 @@
         <v>0</v>
       </c>
       <c r="AG110" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH110" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.99</v>
+        <v>3.31</v>
       </c>
       <c r="Q115" t="n">
-        <v>4.12</v>
+        <v>3.68</v>
       </c>
       <c r="R115" t="n">
-        <v>3.7</v>
+        <v>2.27</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,16 +23107,16 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q157" t="n">
-        <v>6.3</v>
+        <v>3.42</v>
       </c>
       <c r="R157" t="n">
-        <v>11.2</v>
+        <v>2.98</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF168" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF171" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.57</v>
+        <v>4.27</v>
       </c>
       <c r="R182" t="n">
-        <v>1.81</v>
+        <v>5.3</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF182" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF186" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF191" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF192" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH225" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q228" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45374,10 +45374,10 @@
         <v>0</v>
       </c>
       <c r="AG228" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,133 +46308,133 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S233" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T233" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V233" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W233" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X233" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y233" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA233" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB233" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC233" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD233" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE233" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF233" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG233" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH233" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI233" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AJ233" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK233" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL233" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM233" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN233" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO233" t="n">
         <v>0</v>
       </c>
       <c r="AP233" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ233" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR233" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS233" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AU233" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AV233" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW233" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX233" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY233" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ233" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA233" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB233" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC233" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD233" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE233" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF233" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,133 +46505,133 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="R234" t="n">
-        <v>3.4</v>
+        <v>4.16</v>
       </c>
       <c r="S234" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T234" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V234" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W234" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X234" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC234" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD234" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF234" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG234" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="AH234" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI234" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK234" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL234" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM234" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN234" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO234" t="n">
         <v>0</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR234" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS234" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AT234" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW234" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AX234" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AY234" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ234" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA234" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BB234" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC234" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BD234" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE234" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF234" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG234" t="n">
         <v>0</v>
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,133 +46702,133 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q235" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R235" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="S235" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="T235" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="U235" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="V235" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W235" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="X235" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Y235" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z235" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AA235" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB235" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC235" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY235" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD235" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE235" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF235" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG235" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH235" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI235" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ235" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK235" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL235" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM235" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN235" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO235" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP235" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ235" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR235" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS235" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT235" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AU235" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV235" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW235" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX235" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY235" t="n">
+      <c r="AZ235" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BB235" t="n">
         <v>1.17</v>
       </c>
-      <c r="AZ235" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BA235" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB235" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC235" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="BD235" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="BE235" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="BF235" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BG235" t="n">
         <v>0</v>
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,133 +46899,133 @@
         </is>
       </c>
       <c r="P236" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R236" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S236" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T236" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U236" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V236" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W236" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X236" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV236" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q236" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="R236" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="S236" t="n">
-        <v>0</v>
-      </c>
-      <c r="T236" t="n">
-        <v>0</v>
-      </c>
-      <c r="U236" t="n">
-        <v>0</v>
-      </c>
-      <c r="V236" t="n">
-        <v>0</v>
-      </c>
-      <c r="W236" t="n">
-        <v>0</v>
-      </c>
-      <c r="X236" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y236" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV236" t="n">
-        <v>0</v>
-      </c>
       <c r="AW236" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX236" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY236" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ236" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB236" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC236" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD236" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE236" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF236" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,133 +47096,133 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="Q237" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R237" t="n">
-        <v>7.65</v>
+        <v>3.4</v>
       </c>
       <c r="S237" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T237" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U237" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V237" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W237" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X237" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y237" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA237" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB237" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC237" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD237" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE237" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF237" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG237" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="AH237" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI237" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ237" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK237" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL237" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM237" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN237" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO237" t="n">
         <v>0</v>
       </c>
       <c r="AP237" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ237" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR237" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS237" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AU237" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV237" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW237" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AX237" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY237" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ237" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA237" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BB237" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC237" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD237" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE237" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF237" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,133 +47293,133 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="T238" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V238" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W238" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X238" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA238" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB238" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC238" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD238" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF238" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG238" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH238" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI238" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ238" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK238" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL238" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM238" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN238" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO238" t="n">
         <v>0</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR238" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS238" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT238" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AU238" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV238" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW238" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX238" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY238" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ238" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BA238" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BB238" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC238" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD238" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE238" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF238" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,133 +47490,133 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T239" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U239" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V239" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W239" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X239" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA239" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB239" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC239" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD239" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF239" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG239" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH239" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI239" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AJ239" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK239" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL239" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM239" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN239" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO239" t="n">
         <v>0</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR239" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AS239" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AT239" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV239" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW239" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX239" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY239" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ239" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA239" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB239" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC239" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD239" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE239" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF239" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q240" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49111,10 +49111,10 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF247" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG247" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,133 +49460,133 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T249" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V249" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W249" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X249" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB249" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC249" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD249" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF249" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH249" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI249" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ249" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK249" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL249" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM249" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN249" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO249" t="n">
         <v>0</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR249" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS249" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT249" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV249" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW249" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX249" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY249" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ249" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA249" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB249" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC249" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE249" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF249" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,133 +49657,133 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S250" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T250" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U250" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V250" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W250" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X250" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA250" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB250" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC250" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD250" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF250" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG250" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH250" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI250" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ250" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK250" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL250" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM250" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN250" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO250" t="n">
         <v>0</v>
       </c>
       <c r="AP250" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR250" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS250" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU250" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV250" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW250" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX250" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY250" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ250" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA250" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB250" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC250" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE250" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF250" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="R264" t="n">
-        <v>2.84</v>
+        <v>3.39</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52460,10 +52460,10 @@
         <v>0</v>
       </c>
       <c r="AE264" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AF264" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52612,13 +52612,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q265" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -52657,10 +52657,10 @@
         <v>0</v>
       </c>
       <c r="AE265" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF265" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG265" t="n">
         <v>0</v>
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,13 +53006,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q267" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -53051,10 +53051,10 @@
         <v>0</v>
       </c>
       <c r="AE267" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF267" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG267" t="n">
         <v>0</v>
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q276" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55322,22 +55322,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,7 +55519,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q281" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -56110,22 +56110,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF283" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R285" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF285" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q291" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57779,10 +57779,10 @@
         <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF291" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG291" t="n">
         <v>0</v>
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -57976,10 +57976,10 @@
         <v>0</v>
       </c>
       <c r="AE292" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF292" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG292" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="Q303" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="R303" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60143,10 +60143,10 @@
         <v>0</v>
       </c>
       <c r="AE303" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF303" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="Q304" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R304" t="n">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60340,10 +60340,10 @@
         <v>0</v>
       </c>
       <c r="AE304" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AF304" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -60444,7 +60444,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60492,13 +60492,13 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q305" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R305" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
@@ -60537,10 +60537,10 @@
         <v>0</v>
       </c>
       <c r="AE305" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF305" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG305" t="n">
         <v>0</v>
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60689,13 +60689,13 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q306" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R306" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
@@ -60734,10 +60734,10 @@
         <v>0</v>
       </c>
       <c r="AE306" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF306" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG306" t="n">
         <v>0</v>
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="Q307" t="n">
-        <v>3.58</v>
+        <v>6.1</v>
       </c>
       <c r="R307" t="n">
-        <v>3.1</v>
+        <v>6.63</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -60931,10 +60931,10 @@
         <v>0</v>
       </c>
       <c r="AE307" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF307" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG307" t="n">
         <v>0</v>
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61083,13 +61083,13 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q308" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R308" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -61128,10 +61128,10 @@
         <v>0</v>
       </c>
       <c r="AE308" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF308" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG308" t="n">
         <v>0</v>
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61280,13 +61280,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q309" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R309" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,7 +62020,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62217,7 +62217,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,7 +62414,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -62424,12 +62424,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62611,22 +62611,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62655,7 +62655,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -62808,22 +62808,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -62852,7 +62852,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q319" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R319" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63409,12 +63409,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -63447,13 +63447,13 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>3.43</v>
+        <v>1.89</v>
       </c>
       <c r="Q320" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="R320" t="n">
-        <v>2.04</v>
+        <v>3.93</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
@@ -63498,10 +63498,10 @@
         <v>0</v>
       </c>
       <c r="AG320" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH320" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI320" t="n">
         <v>0</v>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q321" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63689,10 +63689,10 @@
         <v>0</v>
       </c>
       <c r="AE321" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF321" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG321" t="n">
         <v>0</v>
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="Q322" t="n">
-        <v>4.03</v>
+        <v>4.58</v>
       </c>
       <c r="R322" t="n">
-        <v>3.93</v>
+        <v>5.82</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,16 +63886,16 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF322" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG322" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH322" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI322" t="n">
         <v>0</v>

--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22325,10 +22325,10 @@
         <v>0</v>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="R113" t="n">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22916,10 +22916,10 @@
         <v>0</v>
       </c>
       <c r="AG114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.31</v>
+        <v>2.65</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="R115" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="R129" t="n">
-        <v>4.07</v>
+        <v>2.98</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28229,10 +28229,10 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF141" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="Q161" t="n">
-        <v>6.3</v>
+        <v>3.64</v>
       </c>
       <c r="R161" t="n">
-        <v>11.2</v>
+        <v>4.22</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF186" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF213" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q226" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44980,10 +44980,10 @@
         <v>0</v>
       </c>
       <c r="AG226" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH226" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI226" t="n">
         <v>0</v>
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>12.7</v>
+        <v>1.48</v>
       </c>
       <c r="Q231" t="n">
-        <v>6.4</v>
+        <v>5.03</v>
       </c>
       <c r="R231" t="n">
-        <v>1.28</v>
+        <v>7.01</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH231" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46311,130 +46311,130 @@
         <v>1.95</v>
       </c>
       <c r="Q233" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R233" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="S233" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="T233" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="U233" t="n">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="V233" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W233" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X233" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y233" t="n">
         <v>1.28</v>
       </c>
-      <c r="W233" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X233" t="n">
+      <c r="Z233" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC233" t="n">
         <v>2.36</v>
       </c>
-      <c r="Y233" t="n">
+      <c r="BD233" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE233" t="n">
         <v>1.51</v>
       </c>
-      <c r="Z233" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA233" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB233" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC233" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD233" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE233" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF233" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG233" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH233" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI233" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AJ233" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK233" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL233" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM233" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN233" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO233" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP233" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ233" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR233" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AS233" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT233" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AU233" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV233" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW233" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX233" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY233" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ233" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA233" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB233" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC233" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD233" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE233" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BF233" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="BG233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,133 +46505,133 @@
         </is>
       </c>
       <c r="P234" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R234" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S234" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T234" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U234" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V234" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W234" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X234" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV234" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q234" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="R234" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="S234" t="n">
-        <v>0</v>
-      </c>
-      <c r="T234" t="n">
-        <v>0</v>
-      </c>
-      <c r="U234" t="n">
-        <v>0</v>
-      </c>
-      <c r="V234" t="n">
-        <v>0</v>
-      </c>
-      <c r="W234" t="n">
-        <v>0</v>
-      </c>
-      <c r="X234" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y234" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV234" t="n">
-        <v>0</v>
-      </c>
       <c r="AW234" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX234" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY234" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ234" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB234" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC234" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD234" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE234" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF234" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG234" t="n">
         <v>0</v>
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,133 +46899,133 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R236" t="n">
-        <v>2.55</v>
+        <v>7.65</v>
       </c>
       <c r="S236" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T236" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U236" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V236" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W236" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X236" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD236" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF236" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG236" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH236" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI236" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK236" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL236" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AM236" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN236" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO236" t="n">
         <v>0</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR236" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AS236" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AT236" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV236" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AW236" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX236" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY236" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ236" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BA236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB236" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC236" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD236" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BE236" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF236" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,133 +47096,133 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q237" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T237" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U237" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V237" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W237" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X237" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB237" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC237" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD237" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF237" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG237" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="AH237" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI237" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK237" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL237" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM237" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN237" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO237" t="n">
         <v>0</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR237" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS237" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AT237" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV237" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW237" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AX237" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AY237" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ237" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA237" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BB237" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC237" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BD237" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE237" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF237" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,133 +47884,133 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S241" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T241" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U241" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V241" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W241" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X241" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y241" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z241" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA241" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB241" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC241" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD241" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF241" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG241" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH241" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI241" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AJ241" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK241" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL241" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM241" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN241" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO241" t="n">
         <v>0</v>
       </c>
       <c r="AP241" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ241" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR241" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS241" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AU241" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AV241" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW241" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX241" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY241" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ241" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA241" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB241" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC241" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD241" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE241" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF241" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG241" t="n">
         <v>0</v>
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q244" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,133 +48672,133 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S245" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T245" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U245" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V245" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W245" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X245" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y245" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA245" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB245" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC245" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD245" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF245" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG245" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH245" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI245" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ245" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK245" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL245" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM245" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN245" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO245" t="n">
         <v>0</v>
       </c>
       <c r="AP245" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ245" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR245" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS245" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU245" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV245" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW245" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX245" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY245" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ245" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA245" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB245" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC245" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE245" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF245" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49111,10 +49111,10 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF247" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG247" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,133 +49657,133 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T250" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U250" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V250" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W250" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X250" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB250" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC250" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD250" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF250" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG250" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH250" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI250" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ250" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK250" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL250" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM250" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN250" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO250" t="n">
         <v>0</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR250" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS250" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT250" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU250" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV250" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW250" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX250" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY250" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ250" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA250" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB250" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC250" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD250" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE250" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF250" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52460,10 +52460,10 @@
         <v>0</v>
       </c>
       <c r="AE264" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF264" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,13 +53006,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="Q267" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="R267" t="n">
-        <v>2.84</v>
+        <v>3.39</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -53051,10 +53051,10 @@
         <v>0</v>
       </c>
       <c r="AE267" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AF267" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG267" t="n">
         <v>0</v>
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,13 +53203,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q268" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -53248,10 +53248,10 @@
         <v>0</v>
       </c>
       <c r="AE268" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF268" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG268" t="n">
         <v>0</v>
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF272" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54233,10 +54233,10 @@
         <v>0</v>
       </c>
       <c r="AE273" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF273" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG273" t="n">
         <v>0</v>
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q278" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55322,22 +55322,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55716,22 +55716,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q281" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R283" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q284" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF284" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56504,22 +56504,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF285" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q291" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R291" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57779,10 +57779,10 @@
         <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF291" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG291" t="n">
         <v>0</v>
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="Q292" t="n">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="R292" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -57976,10 +57976,10 @@
         <v>0</v>
       </c>
       <c r="AE292" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF292" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG292" t="n">
         <v>0</v>
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q293" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="Q303" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="R303" t="n">
-        <v>3.1</v>
+        <v>3.72</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60143,10 +60143,10 @@
         <v>0</v>
       </c>
       <c r="AE303" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF303" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="Q304" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R304" t="n">
-        <v>3.6</v>
+        <v>4.32</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60340,10 +60340,10 @@
         <v>0</v>
       </c>
       <c r="AE304" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AF304" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60492,13 +60492,13 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>1.82</v>
+        <v>2.33</v>
       </c>
       <c r="Q305" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="R305" t="n">
-        <v>4.32</v>
+        <v>3.1</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
@@ -60537,10 +60537,10 @@
         <v>0</v>
       </c>
       <c r="AE305" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AF305" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AG305" t="n">
         <v>0</v>
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q307" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R307" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61083,13 +61083,13 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q308" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R308" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -61128,10 +61128,10 @@
         <v>0</v>
       </c>
       <c r="AE308" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF308" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AF308" t="n">
-        <v>1.9</v>
       </c>
       <c r="AG308" t="n">
         <v>0</v>
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61280,13 +61280,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q309" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R309" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,7 +62020,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62217,7 +62217,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,22 +62414,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62458,7 +62458,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -62611,22 +62611,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62655,7 +62655,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -62808,7 +62808,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>3.43</v>
+        <v>1.56</v>
       </c>
       <c r="Q319" t="n">
-        <v>4.02</v>
+        <v>4.58</v>
       </c>
       <c r="R319" t="n">
-        <v>2.04</v>
+        <v>5.82</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63295,10 +63295,10 @@
         <v>0</v>
       </c>
       <c r="AE319" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF319" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG319" t="n">
         <v>0</v>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q321" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R321" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63793,7 +63793,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q322" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,10 +63886,10 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF322" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG322" t="n">
         <v>0</v>
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64432,13 +64432,13 @@
         </is>
       </c>
       <c r="P325" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q325" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S325" t="n">
         <v>0</v>
@@ -64483,10 +64483,10 @@
         <v>0</v>
       </c>
       <c r="AG325" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH325" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI325" t="n">
         <v>0</v>
@@ -64581,7 +64581,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -64591,12 +64591,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -64629,13 +64629,13 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q326" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="R326" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S326" t="n">
         <v>0</v>
@@ -64680,10 +64680,10 @@
         <v>0</v>
       </c>
       <c r="AG326" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH326" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI326" t="n">
         <v>0</v>

--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2231,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22325,10 +22325,10 @@
         <v>0</v>
       </c>
       <c r="AG111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.31</v>
+        <v>2.65</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="R113" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.65</v>
+        <v>1.54</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.82</v>
+        <v>4.88</v>
       </c>
       <c r="R115" t="n">
-        <v>2.65</v>
+        <v>6.3</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,16 +23107,16 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="R141" t="n">
-        <v>4.07</v>
+        <v>3.77</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28229,10 +28229,10 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AF141" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AG141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF169" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF171" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="R188" t="n">
-        <v>3.64</v>
+        <v>2.9</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH225" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="Q226" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44980,10 +44980,10 @@
         <v>0</v>
       </c>
       <c r="AG226" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI226" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH230" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q231" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH231" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,133 +46308,133 @@
         </is>
       </c>
       <c r="P233" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R233" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T233" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U233" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V233" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W233" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X233" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF233" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q233" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R233" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S233" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T233" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U233" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="V233" t="n">
+      <c r="AG233" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN233" t="n">
         <v>1.46</v>
       </c>
-      <c r="W233" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X233" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y233" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z233" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA233" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB233" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC233" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD233" t="n">
+      <c r="AO233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AS233" t="n">
         <v>2.74</v>
       </c>
-      <c r="AE233" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF233" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG233" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="AH233" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI233" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ233" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK233" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL233" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM233" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN233" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO233" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP233" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ233" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AR233" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS233" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AT233" t="n">
-        <v>5.15</v>
+        <v>3.86</v>
       </c>
       <c r="AU233" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AV233" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AW233" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AX233" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AY233" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AZ233" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="BA233" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="BB233" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BC233" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="BD233" t="n">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
       <c r="BE233" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="BF233" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="BG233" t="n">
         <v>0</v>
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,133 +46505,133 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R234" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="S234" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="T234" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="U234" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="V234" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W234" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="X234" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Y234" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z234" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AA234" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB234" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC234" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY234" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD234" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE234" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF234" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG234" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH234" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI234" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ234" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK234" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL234" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM234" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN234" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP234" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ234" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR234" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS234" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT234" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AU234" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV234" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW234" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX234" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY234" t="n">
+      <c r="AZ234" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BB234" t="n">
         <v>1.17</v>
       </c>
-      <c r="AZ234" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BA234" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB234" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC234" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="BD234" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="BE234" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="BF234" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BG234" t="n">
         <v>0</v>
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,133 +46702,133 @@
         </is>
       </c>
       <c r="P235" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R235" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q235" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R235" t="n">
+      <c r="S235" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U235" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V235" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W235" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X235" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK235" t="n">
         <v>1.91</v>
       </c>
-      <c r="S235" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="T235" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U235" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="V235" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W235" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="X235" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y235" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z235" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA235" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB235" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC235" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD235" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AE235" t="n">
+      <c r="AL235" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV235" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF235" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG235" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH235" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI235" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ235" t="n">
+      <c r="AW235" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY235" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK235" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL235" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM235" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN235" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO235" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP235" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ235" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR235" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS235" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT235" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AU235" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV235" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW235" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX235" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY235" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AZ235" t="n">
-        <v>2.79</v>
+        <v>1.81</v>
       </c>
       <c r="BA235" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="BB235" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BC235" t="n">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="BD235" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="BE235" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="BF235" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="BG235" t="n">
         <v>0</v>
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,133 +46899,133 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R236" t="n">
-        <v>7.65</v>
+        <v>3.1</v>
       </c>
       <c r="S236" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T236" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U236" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V236" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W236" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X236" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y236" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z236" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA236" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB236" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC236" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD236" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE236" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF236" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG236" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH236" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI236" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AJ236" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK236" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL236" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM236" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN236" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO236" t="n">
         <v>0</v>
       </c>
       <c r="AP236" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ236" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR236" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS236" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AU236" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AV236" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW236" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX236" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY236" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ236" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA236" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB236" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC236" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD236" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE236" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF236" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>2.08</v>
+        <v>1.47</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.39</v>
+        <v>3.8</v>
       </c>
       <c r="R239" t="n">
-        <v>4.16</v>
+        <v>7.65</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,133 +47884,133 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T241" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U241" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V241" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W241" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X241" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z241" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA241" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB241" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC241" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD241" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG241" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH241" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI241" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AJ241" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK241" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL241" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM241" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN241" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO241" t="n">
         <v>0</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR241" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AS241" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AT241" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV241" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW241" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX241" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY241" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ241" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA241" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB241" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC241" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD241" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE241" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF241" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG241" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,22 +48230,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,133 +48672,133 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>5.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q245" t="n">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="R245" t="n">
-        <v>1.53</v>
+        <v>3.27</v>
       </c>
       <c r="S245" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T245" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U245" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V245" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W245" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X245" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA245" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC245" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD245" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF245" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AG245" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH245" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI245" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ245" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK245" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL245" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM245" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN245" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO245" t="n">
         <v>0</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR245" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS245" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT245" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU245" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV245" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW245" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX245" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY245" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ245" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA245" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB245" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC245" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD245" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE245" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF245" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,133 +49657,133 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S250" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T250" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U250" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V250" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W250" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X250" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA250" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB250" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC250" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD250" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF250" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG250" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH250" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI250" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ250" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK250" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL250" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM250" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN250" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO250" t="n">
         <v>0</v>
       </c>
       <c r="AP250" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR250" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS250" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU250" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV250" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW250" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX250" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY250" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ250" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA250" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB250" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC250" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE250" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF250" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52612,13 +52612,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q265" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -52657,10 +52657,10 @@
         <v>0</v>
       </c>
       <c r="AE265" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF265" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG265" t="n">
         <v>0</v>
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,13 +53203,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q268" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -53248,10 +53248,10 @@
         <v>0</v>
       </c>
       <c r="AE268" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF268" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG268" t="n">
         <v>0</v>
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF272" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54233,10 +54233,10 @@
         <v>0</v>
       </c>
       <c r="AE273" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF273" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG273" t="n">
         <v>0</v>
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q278" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55322,22 +55322,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q279" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55519,22 +55519,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="R283" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R284" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="Q291" t="n">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="R291" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57779,10 +57779,10 @@
         <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF291" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG291" t="n">
         <v>0</v>
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q292" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q293" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF293" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="Q303" t="n">
-        <v>3.72</v>
+        <v>6.1</v>
       </c>
       <c r="R303" t="n">
-        <v>3.72</v>
+        <v>6.63</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60143,10 +60143,10 @@
         <v>0</v>
       </c>
       <c r="AE303" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF303" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q304" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R304" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60340,10 +60340,10 @@
         <v>0</v>
       </c>
       <c r="AE304" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF304" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60492,13 +60492,13 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>2.33</v>
+        <v>1.82</v>
       </c>
       <c r="Q305" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="R305" t="n">
-        <v>3.1</v>
+        <v>4.32</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
@@ -60537,10 +60537,10 @@
         <v>0</v>
       </c>
       <c r="AE305" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF305" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AG305" t="n">
         <v>0</v>
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60689,13 +60689,13 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q306" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R306" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
@@ -60734,10 +60734,10 @@
         <v>0</v>
       </c>
       <c r="AE306" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF306" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG306" t="n">
         <v>0</v>
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q307" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R307" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -60931,10 +60931,10 @@
         <v>0</v>
       </c>
       <c r="AE307" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF307" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG307" t="n">
         <v>0</v>
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61083,13 +61083,13 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q308" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R308" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -61128,10 +61128,10 @@
         <v>0</v>
       </c>
       <c r="AE308" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF308" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG308" t="n">
         <v>0</v>
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61280,13 +61280,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="Q309" t="n">
-        <v>6.1</v>
+        <v>3.72</v>
       </c>
       <c r="R309" t="n">
-        <v>6.63</v>
+        <v>3.72</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -61325,10 +61325,10 @@
         <v>0</v>
       </c>
       <c r="AE309" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF309" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG309" t="n">
         <v>0</v>
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,22 +62020,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62064,7 +62064,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -62217,7 +62217,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,22 +62414,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62458,7 +62458,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,7 +62808,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1.56</v>
+        <v>3.43</v>
       </c>
       <c r="Q319" t="n">
-        <v>4.58</v>
+        <v>4.02</v>
       </c>
       <c r="R319" t="n">
-        <v>5.82</v>
+        <v>2.04</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63295,10 +63295,10 @@
         <v>0</v>
       </c>
       <c r="AE319" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF319" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG319" t="n">
         <v>0</v>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q321" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63793,7 +63793,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q322" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R322" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,10 +63886,10 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF322" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG322" t="n">
         <v>0</v>
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64432,13 +64432,13 @@
         </is>
       </c>
       <c r="P325" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q325" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="R325" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S325" t="n">
         <v>0</v>
@@ -64483,10 +64483,10 @@
         <v>0</v>
       </c>
       <c r="AG325" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH325" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI325" t="n">
         <v>0</v>
@@ -64581,7 +64581,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -64591,12 +64591,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -64629,13 +64629,13 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q326" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R326" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S326" t="n">
         <v>0</v>
@@ -64680,10 +64680,10 @@
         <v>0</v>
       </c>
       <c r="AG326" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH326" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI326" t="n">
         <v>0</v>

--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.74</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>3.41</v>
+        <v>4.04</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22128,10 +22128,10 @@
         <v>0</v>
       </c>
       <c r="AG110" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.31</v>
+        <v>1.54</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.68</v>
+        <v>4.88</v>
       </c>
       <c r="R112" t="n">
-        <v>2.27</v>
+        <v>6.3</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,16 +22516,16 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="R113" t="n">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,16 +22713,16 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23113,10 +23113,10 @@
         <v>0</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="Q119" t="n">
-        <v>6.3</v>
+        <v>3.48</v>
       </c>
       <c r="R119" t="n">
-        <v>11.2</v>
+        <v>3.77</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28229,10 +28229,10 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG141" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF148" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF163" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF167" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF169" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF171" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF173" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="R187" t="n">
-        <v>3.64</v>
+        <v>2.9</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF187" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF213" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43004,10 +43004,10 @@
         <v>0</v>
       </c>
       <c r="AE216" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF216" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q227" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45177,10 +45177,10 @@
         <v>0</v>
       </c>
       <c r="AG227" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH227" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI227" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1.48</v>
+        <v>12.7</v>
       </c>
       <c r="Q230" t="n">
-        <v>5.03</v>
+        <v>6.4</v>
       </c>
       <c r="R230" t="n">
-        <v>7.01</v>
+        <v>1.28</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,133 +46505,133 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="T234" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V234" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W234" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X234" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC234" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD234" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF234" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG234" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH234" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI234" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK234" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL234" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM234" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN234" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO234" t="n">
         <v>0</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR234" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS234" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT234" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV234" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW234" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX234" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY234" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ234" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BA234" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BB234" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC234" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD234" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE234" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF234" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG234" t="n">
         <v>0</v>
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,133 +46702,133 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q235" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R235" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="S235" t="n">
-        <v>2.43</v>
+        <v>4.28</v>
       </c>
       <c r="T235" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="U235" t="n">
-        <v>4.45</v>
+        <v>2.51</v>
       </c>
       <c r="V235" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W235" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="X235" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Y235" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z235" t="n">
-        <v>8.9</v>
+        <v>6.55</v>
       </c>
       <c r="AA235" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB235" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC235" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AD235" t="n">
-        <v>2.74</v>
+        <v>3.76</v>
       </c>
       <c r="AE235" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AF235" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AG235" t="n">
-        <v>4.08</v>
+        <v>2.97</v>
       </c>
       <c r="AH235" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AI235" t="n">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ235" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK235" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL235" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW235" t="n">
         <v>1.75</v>
       </c>
-      <c r="AM235" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN235" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO235" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP235" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ235" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AR235" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS235" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AT235" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AU235" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV235" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW235" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AX235" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AY235" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AZ235" t="n">
-        <v>1.81</v>
+        <v>2.79</v>
       </c>
       <c r="BA235" t="n">
-        <v>2.56</v>
+        <v>1.58</v>
       </c>
       <c r="BB235" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BC235" t="n">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="BD235" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="BE235" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BF235" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG235" t="n">
         <v>0</v>
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46902,130 +46902,130 @@
         <v>1.95</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R236" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="S236" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="T236" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="U236" t="n">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="V236" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W236" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X236" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y236" t="n">
         <v>1.28</v>
       </c>
-      <c r="W236" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X236" t="n">
+      <c r="Z236" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC236" t="n">
         <v>2.36</v>
       </c>
-      <c r="Y236" t="n">
+      <c r="BD236" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE236" t="n">
         <v>1.51</v>
       </c>
-      <c r="Z236" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA236" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB236" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC236" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD236" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE236" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF236" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG236" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH236" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI236" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AJ236" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK236" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL236" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM236" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN236" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP236" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ236" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR236" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AS236" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT236" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AU236" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV236" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW236" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX236" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY236" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ236" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA236" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB236" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC236" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD236" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE236" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BF236" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="BG236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,133 +47096,133 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q237" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="R237" t="n">
-        <v>4.16</v>
+        <v>3.1</v>
       </c>
       <c r="S237" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T237" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U237" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V237" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W237" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X237" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y237" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA237" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB237" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC237" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD237" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE237" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF237" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG237" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH237" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI237" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AJ237" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK237" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL237" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM237" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN237" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO237" t="n">
         <v>0</v>
       </c>
       <c r="AP237" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ237" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR237" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS237" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AU237" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AV237" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW237" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX237" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY237" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ237" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA237" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB237" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC237" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD237" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE237" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF237" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG237" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q238" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47338,10 +47338,10 @@
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.8</v>
+        <v>3.39</v>
       </c>
       <c r="R239" t="n">
-        <v>7.65</v>
+        <v>4.16</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q240" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48230,22 +48230,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q245" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF245" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,133 +49066,133 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S247" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T247" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U247" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V247" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W247" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X247" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y247" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z247" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA247" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB247" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC247" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD247" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE247" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF247" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG247" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH247" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI247" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ247" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK247" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL247" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM247" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN247" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO247" t="n">
         <v>0</v>
       </c>
       <c r="AP247" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR247" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS247" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU247" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV247" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW247" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX247" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY247" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ247" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA247" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB247" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC247" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD247" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE247" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF247" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG247" t="n">
         <v>0</v>
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,133 +49657,133 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>5.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q250" t="n">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="R250" t="n">
-        <v>1.53</v>
+        <v>3.27</v>
       </c>
       <c r="S250" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T250" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U250" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V250" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W250" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X250" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB250" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC250" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD250" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF250" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AG250" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH250" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI250" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ250" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK250" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL250" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM250" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN250" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO250" t="n">
         <v>0</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR250" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS250" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT250" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU250" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV250" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW250" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX250" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY250" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ250" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA250" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB250" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC250" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD250" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE250" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF250" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q260" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52612,13 +52612,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q265" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -52657,10 +52657,10 @@
         <v>0</v>
       </c>
       <c r="AE265" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF265" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG265" t="n">
         <v>0</v>
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,55 +53006,55 @@
         </is>
       </c>
       <c r="P267" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="n">
+        <v>0</v>
+      </c>
+      <c r="V267" t="n">
+        <v>0</v>
+      </c>
+      <c r="W267" t="n">
+        <v>0</v>
+      </c>
+      <c r="X267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF267" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q267" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R267" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="S267" t="n">
-        <v>0</v>
-      </c>
-      <c r="T267" t="n">
-        <v>0</v>
-      </c>
-      <c r="U267" t="n">
-        <v>0</v>
-      </c>
-      <c r="V267" t="n">
-        <v>0</v>
-      </c>
-      <c r="W267" t="n">
-        <v>0</v>
-      </c>
-      <c r="X267" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y267" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z267" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA267" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB267" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC267" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD267" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE267" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF267" t="n">
-        <v>2.2</v>
       </c>
       <c r="AG267" t="n">
         <v>0</v>
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,13 +53203,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q268" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -53248,10 +53248,10 @@
         <v>0</v>
       </c>
       <c r="AE268" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF268" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG268" t="n">
         <v>0</v>
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF272" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54233,10 +54233,10 @@
         <v>0</v>
       </c>
       <c r="AE273" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF273" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG273" t="n">
         <v>0</v>
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55322,22 +55322,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q279" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55519,22 +55519,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R283" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56504,22 +56504,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF285" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="Q291" t="n">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="R291" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57779,10 +57779,10 @@
         <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF291" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG291" t="n">
         <v>0</v>
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="Q293" t="n">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="R293" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF293" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q304" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60340,10 +60340,10 @@
         <v>0</v>
       </c>
       <c r="AE304" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF304" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q307" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="R307" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -60931,10 +60931,10 @@
         <v>0</v>
       </c>
       <c r="AE307" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AF307" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AG307" t="n">
         <v>0</v>
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61280,13 +61280,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q309" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R309" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -61325,10 +61325,10 @@
         <v>0</v>
       </c>
       <c r="AE309" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF309" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG309" t="n">
         <v>0</v>
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -62020,22 +62020,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62064,7 +62064,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,22 +62414,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62458,7 +62458,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q319" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q321" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R321" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>

--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>4.68</v>
+        <v>4.04</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2231,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="R111" t="n">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AF111" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.88</v>
+        <v>4.12</v>
       </c>
       <c r="R112" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22522,10 +22522,10 @@
         <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.31</v>
+        <v>1.54</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.68</v>
+        <v>4.88</v>
       </c>
       <c r="R114" t="n">
-        <v>2.27</v>
+        <v>6.3</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,16 +22910,16 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="R119" t="n">
-        <v>3.77</v>
+        <v>4.58</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF148" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF163" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF165" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF166" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF167" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF173" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF185" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF187" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="R189" t="n">
-        <v>3.64</v>
+        <v>2.9</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF189" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43004,10 +43004,10 @@
         <v>0</v>
       </c>
       <c r="AE216" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF216" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,10 +43792,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF220" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45177,10 +45177,10 @@
         <v>0</v>
       </c>
       <c r="AG227" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI227" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>12.7</v>
+        <v>1.48</v>
       </c>
       <c r="Q230" t="n">
-        <v>6.4</v>
+        <v>5.03</v>
       </c>
       <c r="R230" t="n">
-        <v>1.28</v>
+        <v>7.01</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH231" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,133 +46308,133 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q233" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R233" t="n">
-        <v>2.55</v>
+        <v>7.65</v>
       </c>
       <c r="S233" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T233" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U233" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V233" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W233" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X233" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB233" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC233" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD233" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF233" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG233" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH233" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI233" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK233" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL233" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AM233" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN233" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO233" t="n">
         <v>0</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR233" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AS233" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AT233" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV233" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AW233" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX233" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY233" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ233" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BA233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB233" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC233" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD233" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BE233" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF233" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,133 +46505,133 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S234" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T234" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U234" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V234" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W234" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X234" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y234" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB234" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC234" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD234" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE234" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF234" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG234" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH234" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI234" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ234" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK234" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL234" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM234" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN234" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO234" t="n">
         <v>0</v>
       </c>
       <c r="AP234" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR234" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS234" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AU234" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV234" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW234" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX234" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY234" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ234" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB234" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC234" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD234" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE234" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF234" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG234" t="n">
         <v>0</v>
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46698,137 +46698,137 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P235" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R235" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q235" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R235" t="n">
+      <c r="S235" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U235" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V235" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W235" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X235" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK235" t="n">
         <v>1.91</v>
       </c>
-      <c r="S235" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="T235" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U235" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="V235" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W235" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="X235" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y235" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z235" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA235" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB235" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC235" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD235" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AE235" t="n">
+      <c r="AL235" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV235" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF235" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG235" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH235" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI235" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ235" t="n">
+      <c r="AW235" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY235" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK235" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL235" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM235" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN235" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO235" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP235" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ235" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR235" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS235" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT235" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AU235" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV235" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW235" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX235" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY235" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AZ235" t="n">
-        <v>2.79</v>
+        <v>1.81</v>
       </c>
       <c r="BA235" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="BB235" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BC235" t="n">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="BD235" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="BE235" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="BF235" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="BG235" t="n">
         <v>0</v>
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,133 +46899,133 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R236" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="S236" t="n">
-        <v>2.43</v>
+        <v>4.28</v>
       </c>
       <c r="T236" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="U236" t="n">
-        <v>4.45</v>
+        <v>2.51</v>
       </c>
       <c r="V236" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W236" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="X236" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Y236" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z236" t="n">
-        <v>8.9</v>
+        <v>6.55</v>
       </c>
       <c r="AA236" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB236" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AD236" t="n">
-        <v>2.74</v>
+        <v>3.76</v>
       </c>
       <c r="AE236" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AF236" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AG236" t="n">
-        <v>4.08</v>
+        <v>2.97</v>
       </c>
       <c r="AH236" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AI236" t="n">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ236" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK236" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL236" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW236" t="n">
         <v>1.75</v>
       </c>
-      <c r="AM236" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN236" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP236" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ236" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AR236" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS236" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AT236" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AU236" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV236" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW236" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AX236" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AY236" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AZ236" t="n">
-        <v>1.81</v>
+        <v>2.79</v>
       </c>
       <c r="BA236" t="n">
-        <v>2.56</v>
+        <v>1.58</v>
       </c>
       <c r="BB236" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BC236" t="n">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="BD236" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="BE236" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BF236" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG236" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.68</v>
+        <v>3.39</v>
       </c>
       <c r="R238" t="n">
-        <v>3.27</v>
+        <v>4.16</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47338,10 +47338,10 @@
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="R240" t="n">
-        <v>7.65</v>
+        <v>3.27</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47732,10 +47732,10 @@
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG240" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,133 +49066,133 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>5.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q247" t="n">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="R247" t="n">
-        <v>1.53</v>
+        <v>3.27</v>
       </c>
       <c r="S247" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T247" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U247" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V247" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W247" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X247" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB247" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC247" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD247" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF247" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AG247" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH247" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI247" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ247" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK247" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL247" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM247" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN247" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO247" t="n">
         <v>0</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ247" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR247" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS247" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT247" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU247" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV247" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW247" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX247" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY247" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ247" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA247" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB247" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC247" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD247" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE247" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF247" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG247" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49456,137 +49456,137 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S249" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T249" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U249" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V249" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W249" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X249" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y249" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z249" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA249" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB249" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC249" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD249" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE249" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF249" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG249" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH249" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI249" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ249" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK249" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL249" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM249" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN249" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO249" t="n">
         <v>0</v>
       </c>
       <c r="AP249" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ249" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR249" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS249" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU249" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV249" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW249" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX249" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY249" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ249" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA249" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB249" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC249" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD249" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE249" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF249" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF250" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q261" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,13 +53203,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q268" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -53248,10 +53248,10 @@
         <v>0</v>
       </c>
       <c r="AE268" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF268" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG268" t="n">
         <v>0</v>
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53400,13 +53400,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q269" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
@@ -53445,10 +53445,10 @@
         <v>0</v>
       </c>
       <c r="AE269" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF269" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG269" t="n">
         <v>0</v>
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q277" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q278" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55519,7 +55519,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -56110,22 +56110,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q284" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF284" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q291" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57779,10 +57779,10 @@
         <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF291" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG291" t="n">
         <v>0</v>
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="Q293" t="n">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="R293" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF293" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="Q303" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="R303" t="n">
-        <v>6.63</v>
+        <v>3.6</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60143,10 +60143,10 @@
         <v>0</v>
       </c>
       <c r="AE303" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF303" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="Q304" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="R304" t="n">
-        <v>3.6</v>
+        <v>6.63</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60340,10 +60340,10 @@
         <v>0</v>
       </c>
       <c r="AE304" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF304" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -60444,7 +60444,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60492,13 +60492,13 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q305" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R305" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
@@ -60537,10 +60537,10 @@
         <v>0</v>
       </c>
       <c r="AE305" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF305" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG305" t="n">
         <v>0</v>
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60689,13 +60689,13 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q306" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R306" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
@@ -60734,10 +60734,10 @@
         <v>0</v>
       </c>
       <c r="AE306" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF306" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG306" t="n">
         <v>0</v>
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="Q307" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="R307" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -60931,10 +60931,10 @@
         <v>0</v>
       </c>
       <c r="AE307" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF307" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG307" t="n">
         <v>0</v>
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61083,13 +61083,13 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q308" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R308" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -61128,10 +61128,10 @@
         <v>0</v>
       </c>
       <c r="AE308" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF308" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG308" t="n">
         <v>0</v>
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61280,13 +61280,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q309" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R309" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -61325,10 +61325,10 @@
         <v>0</v>
       </c>
       <c r="AE309" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF309" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG309" t="n">
         <v>0</v>
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -62020,7 +62020,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62217,7 +62217,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62414,22 +62414,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62458,7 +62458,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,22 +62808,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -62852,7 +62852,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q319" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R319" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63295,10 +63295,10 @@
         <v>0</v>
       </c>
       <c r="AE319" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF319" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG319" t="n">
         <v>0</v>
@@ -63409,12 +63409,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -63447,13 +63447,13 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>1.89</v>
+        <v>3.43</v>
       </c>
       <c r="Q320" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="R320" t="n">
-        <v>3.93</v>
+        <v>2.04</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
@@ -63498,10 +63498,10 @@
         <v>0</v>
       </c>
       <c r="AG320" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH320" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI320" t="n">
         <v>0</v>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q321" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="Q322" t="n">
-        <v>4.58</v>
+        <v>4.03</v>
       </c>
       <c r="R322" t="n">
-        <v>5.82</v>
+        <v>3.93</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,16 +63886,16 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF322" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG322" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH322" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI322" t="n">
         <v>0</v>

--- a/jogos_2026-04-11.xlsx
+++ b/jogos_2026-04-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="R3" t="n">
-        <v>3.41</v>
+        <v>4.68</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2231,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.65</v>
+        <v>1.54</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.82</v>
+        <v>4.88</v>
       </c>
       <c r="R110" t="n">
-        <v>2.65</v>
+        <v>6.3</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,16 +22122,16 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22522,10 +22522,10 @@
         <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.54</v>
+        <v>2.65</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="R114" t="n">
-        <v>6.3</v>
+        <v>2.65</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,16 +22910,16 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF147" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF165" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF177" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,10 +43792,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF220" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH225" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45768,10 +45768,10 @@
         <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>12.7</v>
+        <v>1.48</v>
       </c>
       <c r="Q231" t="n">
-        <v>6.4</v>
+        <v>5.03</v>
       </c>
       <c r="R231" t="n">
-        <v>1.28</v>
+        <v>7.01</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45965,10 +45965,10 @@
         <v>0</v>
       </c>
       <c r="AG231" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH231" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI231" t="n">
         <v>0</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q233" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,133 +46899,133 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R236" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="S236" t="n">
-        <v>4.28</v>
+        <v>2.62</v>
       </c>
       <c r="T236" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="U236" t="n">
-        <v>2.51</v>
+        <v>3.92</v>
       </c>
       <c r="V236" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W236" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X236" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AU236" t="n">
         <v>2.98</v>
       </c>
-      <c r="X236" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y236" t="n">
+      <c r="AV236" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX236" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z236" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA236" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB236" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC236" t="n">
+      <c r="AY236" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD236" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AE236" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF236" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG236" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH236" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI236" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ236" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK236" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL236" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM236" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN236" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO236" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP236" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ236" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR236" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS236" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT236" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AU236" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV236" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW236" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX236" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY236" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AZ236" t="n">
-        <v>2.79</v>
+        <v>1.58</v>
       </c>
       <c r="BA236" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="BB236" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC236" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="BD236" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="BE236" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="BF236" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="BG236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,133 +47096,133 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q237" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T237" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U237" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V237" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W237" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X237" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB237" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC237" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD237" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF237" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG237" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH237" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI237" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK237" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL237" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM237" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN237" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO237" t="n">
         <v>0</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR237" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AS237" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AT237" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV237" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW237" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX237" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY237" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ237" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA237" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB237" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC237" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD237" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE237" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF237" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,133 +47293,133 @@
         </is>
       </c>
       <c r="P238" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R238" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S238" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="T238" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U238" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="V238" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W238" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="X238" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL238" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q238" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="R238" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="S238" t="n">
-        <v>0</v>
-      </c>
-      <c r="T238" t="n">
-        <v>0</v>
-      </c>
-      <c r="U238" t="n">
-        <v>0</v>
-      </c>
-      <c r="V238" t="n">
-        <v>0</v>
-      </c>
-      <c r="W238" t="n">
-        <v>0</v>
-      </c>
-      <c r="X238" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y238" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK238" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL238" t="n">
-        <v>0</v>
-      </c>
       <c r="AM238" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN238" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO238" t="n">
         <v>0</v>
       </c>
       <c r="AP238" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ238" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR238" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS238" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AU238" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV238" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW238" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX238" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY238" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ238" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BA238" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BB238" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC238" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD238" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE238" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF238" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG238" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49259,137 +49259,137 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S248" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="T248" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U248" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V248" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W248" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X248" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA248" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB248" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC248" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD248" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG248" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH248" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI248" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ248" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK248" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL248" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM248" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN248" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO248" t="n">
         <v>0</v>
       </c>
       <c r="AP248" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ248" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR248" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS248" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AU248" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV248" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW248" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX248" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY248" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ248" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BA248" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB248" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC248" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD248" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE248" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF248" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49456,137 +49456,137 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P249" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="T249" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V249" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W249" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X249" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB249" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC249" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD249" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF249" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH249" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI249" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ249" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK249" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL249" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM249" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN249" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO249" t="n">
         <v>0</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR249" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS249" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT249" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AV249" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW249" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX249" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY249" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ249" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BA249" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB249" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC249" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE249" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF249" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG249" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52460,10 +52460,10 @@
         <v>0</v>
       </c>
       <c r="AE264" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF264" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52612,13 +52612,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q265" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -52657,10 +52657,10 @@
         <v>0</v>
       </c>
       <c r="AE265" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF265" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG265" t="n">
         <v>0</v>
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,13 +53006,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q267" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -53051,10 +53051,10 @@
         <v>0</v>
       </c>
       <c r="AE267" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF267" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG267" t="n">
         <v>0</v>
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53400,13 +53400,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q269" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
@@ -53445,10 +53445,10 @@
         <v>0</v>
       </c>
       <c r="AE269" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF269" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG269" t="n">
         <v>0</v>
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF272" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54233,10 +54233,10 @@
         <v>0</v>
       </c>
       <c r="AE273" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF273" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG273" t="n">
         <v>0</v>
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q278" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,7 +55519,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,22 +55716,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q281" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -56110,22 +56110,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF283" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R285" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF285" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,7 +57686,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q291" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R291" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q292" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59507,13 +59507,13 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q300" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R300" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -59552,10 +59552,10 @@
         <v>0</v>
       </c>
       <c r="AE300" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF300" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG300" t="n">
         <v>0</v>
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="Q303" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="R303" t="n">
-        <v>3.6</v>
+        <v>6.63</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60143,10 +60143,10 @@
         <v>0</v>
       </c>
       <c r="AE303" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF303" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q304" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R304" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60444,7 +60444,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60689,13 +60689,13 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q306" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R306" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
@@ -60734,10 +60734,10 @@
         <v>0</v>
       </c>
       <c r="AE306" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF306" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG306" t="n">
         <v>0</v>
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -60886,13 +60886,13 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="Q307" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="R307" t="n">
-        <v>3.1</v>
+        <v>3.72</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -60931,10 +60931,10 @@
         <v>0</v>
       </c>
       <c r="AE307" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF307" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG307" t="n">
         <v>0</v>
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61083,13 +61083,13 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="Q308" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="R308" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -61128,10 +61128,10 @@
         <v>0</v>
       </c>
       <c r="AE308" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF308" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG308" t="n">
         <v>0</v>
@@ -61429,22 +61429,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61473,7 +61473,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62020,7 +62020,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62217,7 +62217,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62621,12 +62621,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -62808,22 +62808,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -62852,7 +62852,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -63015,12 +63015,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -63202,7 +63202,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -63212,12 +63212,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -63250,13 +63250,13 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q319" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -63295,10 +63295,10 @@
         <v>0</v>
       </c>
       <c r="AE319" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF319" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG319" t="n">
         <v>0</v>
@@ -63409,12 +63409,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -63447,13 +63447,13 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>3.43</v>
+        <v>1.89</v>
       </c>
       <c r="Q320" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="R320" t="n">
-        <v>2.04</v>
+        <v>3.93</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
@@ -63498,10 +63498,10 @@
         <v>0</v>
       </c>
       <c r="AG320" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH320" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI320" t="n">
         <v>0</v>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -63606,12 +63606,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -63644,13 +63644,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q321" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R321" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -63803,12 +63803,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -63841,13 +63841,13 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="Q322" t="n">
-        <v>4.03</v>
+        <v>4.58</v>
       </c>
       <c r="R322" t="n">
-        <v>3.93</v>
+        <v>5.82</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -63886,16 +63886,16 @@
         <v>0</v>
       </c>
       <c r="AE322" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF322" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG322" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH322" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI322" t="n">
         <v>0</v>
@@ -64384,7 +64384,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -64394,12 +64394,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -64432,13 +64432,13 @@
         </is>
       </c>
       <c r="P325" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q325" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S325" t="n">
         <v>0</v>
@@ -64483,10 +64483,10 @@
         <v>0</v>
       </c>
       <c r="AG325" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH325" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI325" t="n">
         <v>0</v>
@@ -64581,7 +64581,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -64591,12 +64591,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -64629,13 +64629,13 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q326" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="R326" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S326" t="n">
         <v>0</v>
@@ -64680,10 +64680,10 @@
         <v>0</v>
       </c>
       <c r="AG326" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH326" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI326" t="n">
         <v>0</v>
